--- a/apps/api/assets/vocabulary/小学/人教版/四年级下.xlsx
+++ b/apps/api/assets/vocabulary/小学/人教版/四年级下.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D105"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -499,6 +499,16 @@
           <t>second floor</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈美〉二楼；〈英〉三楼
@@ -512,6 +522,16 @@
           <t>teacher's office</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -568,6 +588,16 @@
           <t>computer room</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 计算机机房；计算机室
@@ -581,6 +611,16 @@
           <t>art room</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 绘画教室；美术室；美术教室</t>
@@ -593,6 +633,16 @@
           <t>music room</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 音乐教室；音乐室；音乐厅</t>
@@ -603,6 +653,16 @@
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>next to</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -738,6 +798,16 @@
           <t>English class</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 英语课；英文课；英语课程</t>
@@ -774,6 +844,16 @@
           <t>music class</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -786,6 +866,16 @@
           <t>PE class</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -844,6 +934,16 @@
           <t>go to school</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 到校上课；上学去；开始求学
@@ -857,6 +957,16 @@
           <t>go home</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 回家；〈口〉死；(忠告等)刻骨铭心；击中
@@ -868,6 +978,16 @@
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>go to bed</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -934,6 +1054,16 @@
           <t>o'clock</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t>abbr. …点钟（等于of the clock）</t>
@@ -1019,6 +1149,16 @@
           <t>come on</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (演员)出台；进行(很好)；(暴风雨等)起；(病,苦痛等)加深
@@ -1030,6 +1170,16 @@
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>just a minute</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1284,6 +1434,16 @@
           <t>be careful</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 小心；当心；注意</t>
@@ -1322,6 +1482,16 @@
           <t>New York</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【城】纽约州
@@ -1333,6 +1503,16 @@
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>how about</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1573,6 +1753,16 @@
           <t>green beans</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【食】青豆
@@ -2451,6 +2641,16 @@
           <t>try on</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 试穿；〈非正式〉搞恶作剧(以试探能否被容忍)；〈非正式〉耍花招
@@ -2489,6 +2689,16 @@
           <t>of course</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 当然
